--- a/Data/Building/Context.Weather.xlsx
+++ b/Data/Building/Context.Weather.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709264894</v>
+        <v>1711857786</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709285878</v>
+        <v>1711876478</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709236030</v>
+        <v>1711935217</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709250217</v>
+        <v>1711990235</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709254551</v>
+        <v>1711993941</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709263270</v>
+        <v>1712000431</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +667,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709345677</v>
+        <v>1712016527</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709396636</v>
+        <v>1712021051</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709430126</v>
+        <v>1712029747</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +766,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709450711</v>
+        <v>1712111962</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +799,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709492507</v>
+        <v>1712216449</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +832,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709508165</v>
+        <v>1712257954</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +865,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709512806</v>
+        <v>1712271803</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +898,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709521698</v>
+        <v>1712276729</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +931,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709533994</v>
+        <v>1712285531</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +964,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709569799</v>
+        <v>1712371643</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +997,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709605308</v>
+        <v>1712421979</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1030,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709744875</v>
+        <v>1712460629</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1063,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709748580</v>
+        <v>1712593516</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709754137</v>
+        <v>1712628193</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709770587</v>
+        <v>1712645734</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709775928</v>
+        <v>1712682418</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709785907</v>
+        <v>1712686569</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709860859</v>
+        <v>1712694014</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709915684</v>
+        <v>1712709677</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709948267</v>
+        <v>1712713702</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1327,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709966554</v>
+        <v>1712722089</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710037367</v>
+        <v>1712802980</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710088486</v>
+        <v>1712819030</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710124870</v>
+        <v>1712888329</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710174588</v>
+        <v>1713000446</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1496,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710208607</v>
+        <v>1713064215</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1529,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710261253</v>
+        <v>1713116010</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710297486</v>
+        <v>1713122622</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1595,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710348814</v>
+        <v>1713137279</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1624,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710352315</v>
+        <v>1713141376</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1657,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710358253</v>
+        <v>1713149643</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1649,10 +1690,11 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710375695</v>
+        <v>1713231002</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1723,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710381665</v>
+        <v>1713285236</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1756,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710392830</v>
+        <v>1713318555</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1789,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710409600</v>
+        <v>1713375420</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1822,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710434366</v>
+        <v>1713381599</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1855,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710467813</v>
+        <v>1713395513</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1888,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710486887</v>
+        <v>1713399434</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1921,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710552839</v>
+        <v>1713406631</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1954,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: cloudy</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710607025</v>
+        <v>1713418392</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +1987,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710642639</v>
+        <v>1713491483</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2024,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710661272</v>
+        <v>1713544757</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710726851</v>
+        <v>1713579872</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710743134</v>
+        <v>1713689636</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710814043</v>
+        <v>1713750076</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710833065</v>
+        <v>1713807530</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710903785</v>
+        <v>1713814140</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710929713</v>
+        <v>1713829309</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710990796</v>
+        <v>1713834077</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2284,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1711016978</v>
+        <v>1713842880</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1711040361</v>
+        <v>1713854573</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2354,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1711044064</v>
+        <v>1713923752</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2383,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Context.Weather.state: cloudy</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1711050122</v>
+        <v>1713977314</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2416,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1711064604</v>
+        <v>1713980654</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1711069179</v>
+        <v>1713986410</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2482,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Context.Weather.state: raining</t>
+          <t>Context.Weather.state: sunny</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1711078115</v>
+        <v>1713999852</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2519,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1711159029</v>
+        <v>1714003067</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2548,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1711266667</v>
+        <v>1714010491</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2585,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1711331432</v>
+        <v>1714063649</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2614,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1711350402</v>
+        <v>1714067318</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2651,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1711418727</v>
+        <v>1714073429</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1711471610</v>
+        <v>1714087336</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2717,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1711509878</v>
+        <v>1714090653</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2746,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1711532889</v>
+        <v>1714097857</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2783,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1711597642</v>
+        <v>1714109728</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2812,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Context.Weather.state: sunny</t>
+          <t>Context.Weather.state: raining</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1711620641</v>
+        <v>1714148848</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2849,139 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Weather_Change</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1714184789</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Context.Weather.state: sunny</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Weather_Change</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1714206849</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Context.Weather.state: cloudy</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Weather_Change</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1714271540</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Context.Weather.state: sunny</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Weather_Change</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1714291796</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Context.Weather.state: cloudy</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
